--- a/sources/metaPee/combined/provisional_ui/subexposure_views/yes/Plot/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/sources/metaPee/combined/provisional_ui/subexposure_views/yes/Plot/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -891,141 +891,141 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>beta_carotene</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.7557081668603727</v>
+        <v>0.7499115595537207</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.6375643919946457</v>
+        <v>0.6812676670885198</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.8956549863849572</v>
+        <v>0.8253894033052035</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.4498278062406948</v>
+        <v>0.5066166105770156</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1.269585440331544</v>
+        <v>1.110045220411901</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>881922</v>
+        <v>14136959</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>4765</v>
+        <v>29867</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>vitamin_c</t>
+          <t>beta_carotene</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.7590406087904665</v>
+        <v>0.7557081668603727</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.6146514007082959</v>
+        <v>0.6375643919946457</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.9373486257886696</v>
+        <v>0.8956549863849572</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.4240450272610667</v>
+        <v>0.4498278062406948</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.358682707622687</v>
+        <v>1.269585440331544</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>128222</v>
+        <v>881922</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2559</v>
+        <v>4765</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>vitamin_c</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.7716686738745262</v>
+        <v>0.7590406087904665</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.6812676670885198</v>
+        <v>0.6146514007082959</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.8741528788765721</v>
+        <v>0.9373486257886696</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.630272139746614</v>
+        <v>0.4240450272610667</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.9447863941418472</v>
+        <v>1.358682707622687</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>881922</v>
+        <v>128222</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4765</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.7761573567801574</v>
+        <v>0.7716686738745262</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.7136233334718519</v>
+        <v>0.6812676670885198</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.8440867544803625</v>
+        <v>0.8741528788765721</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.5466939039856373</v>
+        <v>0.630272139746614</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.101933345318201</v>
+        <v>0.9447863941418472</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>14497576</v>
+        <v>881922</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>30798</v>
+        <v>4765</v>
       </c>
     </row>
     <row r="18">
@@ -1446,121 +1446,121 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>potassium</t>
+          <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1.099713607906872</v>
+        <v>1.105391974364155</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.8702945807931509</v>
+        <v>0.9570496576537233</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1.388589318228265</v>
-      </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
+        <v>1.276599624884141</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.2118725844161015</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>5.767104886911577</v>
+      </c>
       <c r="H31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="2" t="n">
-        <v>120852</v>
+        <v>563999</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>485</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sugar_sweetened_beverage_intake</t>
+          <t>processed_meat_intake</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1.105391974364155</v>
+        <v>1.149239018159417</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.9570496576537233</v>
+        <v>0.9369737613162469</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1.276599624884141</v>
+        <v>1.409591575973965</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.2118725844161015</v>
+        <v>0.6296319129363084</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>5.767104886911577</v>
+        <v>2.09765466731294</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="2" t="n">
-        <v>563999</v>
+        <v>1766660</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1503</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>processed_meat_intake</t>
+          <t>ultra_processed_food_intake</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1.149239018159417</v>
+        <v>1.159516828778204</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.9369737613162469</v>
+        <v>1.049863300995226</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1.409591575973965</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0.6296319129363084</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>2.09765466731294</v>
-      </c>
+        <v>1.289026327823149</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="2" t="n">
-        <v>1766660</v>
+        <v>480347</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>5212</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ultra_processed_food_intake</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.159516828778204</v>
+        <v>1.198753536073191</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1.049863300995226</v>
+        <v>0.920382805616512</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.289026327823149</v>
+        <v>1.575249959766321</v>
       </c>
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr"/>
@@ -1569,29 +1569,29 @@
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="2" t="n">
-        <v>480347</v>
+        <v>1811</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>3330</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.198753536073191</v>
+        <v>1.225562595253664</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.920382805616512</v>
+        <v>0.5280311504245172</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1.575249959766321</v>
+        <v>2.844820578397655</v>
       </c>
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr"/>
@@ -1600,29 +1600,29 @@
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
-        <v>1811</v>
+        <v>4597</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>9</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>manganese</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.225562595253664</v>
+        <v>1.259147309219077</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.5280311504245172</v>
+        <v>0.8303675352604869</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2.844820578397655</v>
+        <v>1.905481103347211</v>
       </c>
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr"/>
@@ -1631,29 +1631,29 @@
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
-        <v>4597</v>
+        <v>61321</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1909</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>manganese</t>
+          <t>potassium</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1.259147309219077</v>
+        <v>1.279067174104721</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.8303675352604869</v>
+        <v>0.8702945807931509</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1.905481103347211</v>
+        <v>1.895554083552581</v>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr"/>
@@ -1662,10 +1662,10 @@
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="2" t="n">
-        <v>61321</v>
+        <v>120852</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>229</v>
+        <v>485</v>
       </c>
     </row>
     <row r="38">
